--- a/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
@@ -529,6 +529,9 @@
       <c r="A11" t="str">
         <v>5</v>
       </c>
+      <c r="C11" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
@@ -532,6 +532,9 @@
       <c r="C11" t="str">
         <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -590,7 +593,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0820151020150201981800</v>
+        <v>08201510201502019818014</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -536,9 +536,95 @@
         <v>14</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>276_情迷罗拉_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>6</v>
+      </c>
+      <c r="C15" t="str">
+        <v>104_绣球重瓣紫_Hydrangea Purple D_Hydrangea L._1stem</v>
+      </c>
+      <c r="F15" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>114_绣球孔雀蓝_Hydrangea Peacoke_Hydrangea L._1stem</v>
+      </c>
+      <c r="F17" t="str">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F18" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>111_绣球紫粉_Hydrangea Purple&amp;Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F19" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>7</v>
+      </c>
+      <c r="C20" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F21" t="str">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -593,7 +679,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08201510201502019818014</v>
+        <v>082015102015020198180141730305023650502016</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -622,9 +622,89 @@
         <v>16</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>528_五代果_pig face_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>506_紫罗兰香槟色_violet champagne_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>8</v>
+      </c>
+      <c r="C27" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>506_紫罗兰香槟色_violet champagne_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -679,7 +759,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>082015102015020198180141730305023650502016</v>
+        <v>0820151020150201981801417303050236505020161820151010131911130</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
@@ -701,6 +701,9 @@
       <c r="C31" t="str">
         <v>506_紫罗兰香槟色_violet champagne_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -759,7 +762,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0820151020150201981801417303050236505020161820151010131911130</v>
+        <v>08201510201502019818014173030502365050201618201510101319111310</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -705,9 +705,95 @@
         <v>10</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>9</v>
+      </c>
+      <c r="C33" t="str">
+        <v>111_绣球紫粉_Hydrangea Purple&amp;Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F33" t="str">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>10</v>
+      </c>
+      <c r="C34" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>455_粉星花_tweedia pink_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>300_白星_White Gypso_ gypsophila_1kg</v>
+      </c>
+      <c r="F39" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>11</v>
+      </c>
+      <c r="C40" t="str">
+        <v>406_千鸟飞燕 白_larkspur white_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>500_千鸟飞燕 粉_larkspur pink_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -762,7 +848,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08201510201502019818014173030502365050201618201510101319111310</v>
+        <v>08201510201502019818014173030502365050201618201510101319111310355130135402120120</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
@@ -790,6 +790,9 @@
       <c r="C41" t="str">
         <v>500_千鸟飞燕 粉_larkspur pink_undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -848,7 +851,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08201510201502019818014173030502365050201618201510101319111310355130135402120120</v>
+        <v>082015102015020198180141730305023650502016182015101013191113103551301354021201210</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -794,9 +794,89 @@
         <v>10</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>492_细米花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>12</v>
+      </c>
+      <c r="C44" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>738_鸢尾花蓝_undefined_undefined_1bunch</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>13</v>
+      </c>
+      <c r="C46" t="str">
+        <v>394_矢车菊_Cornflower_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>394_矢车菊_Cornflower_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>394_矢车菊_Cornflower_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>394_矢车菊_Cornflower_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>469_络新妇粉_Astilbe pink_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>860_大菊白_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -851,7 +931,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>082015102015020198180141730305023650502016182015101013191113103551301354021201210</v>
+        <v>08201510201502019818014173030502365050201618201510101319111310355130135402120121030204001013102100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-4.xlsx
@@ -873,6 +873,9 @@
       <c r="C51" t="str">
         <v>860_大菊白_undefined_undefined_1bunch</v>
       </c>
+      <c r="F51" t="str">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -931,7 +934,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08201510201502019818014173030502365050201618201510101319111310355130135402120121030204001013102100</v>
+        <v>082015102015020198180141730305023650502016182015101013191113103551301354021201210302040010131021012</v>
       </c>
     </row>
   </sheetData>
